--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.121492838136569</v>
+        <v>-0.03866731778013099</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2600020647954149</v>
+        <v>0.1633618824504434</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.5704859829342847</v>
+        <v>-0.2825780153017908</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.8461821644556015</v>
+        <v>-0.3920379268821462</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1589259288842544</v>
+        <v>0.1681073189447396</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8704731294545067</v>
+        <v>-0.2592670374187365</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>54.96614855954268</v>
+        <v>25.89983522561227</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.3714300659463573</v>
+        <v>-0.113024456913173</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2382535239361357</v>
+        <v>0.2761419722571054</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.97078539803066</v>
+        <v>-0.3689639173414205</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-2.485070897550286</v>
+        <v>-0.5306914947627651</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3959997399147833</v>
+        <v>0.1990402017455031</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9681193955094365</v>
+        <v>-0.5898784722603573</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>57.86745753008121</v>
+        <v>47.79494174611592</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1173584346152997</v>
+        <v>-0.1119938263665951</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2005203455874412</v>
+        <v>0.2261208430457188</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.6226070766209734</v>
+        <v>-0.4997428535165224</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.8811363758902642</v>
+        <v>-0.6728143421812479</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2667522594166244</v>
+        <v>0.2224481839167435</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.4569776918822959</v>
+        <v>-0.5230053565383961</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>57.99781740391308</v>
+        <v>60.41137097660307</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1128119732957402</v>
+        <v>-0.000991156312649788</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2472957391828864</v>
+        <v>0.3309252731961395</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.4423257102683749</v>
+        <v>0.11591171748874</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.6781988199922836</v>
+        <v>0.1706461377232188</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2260730895919314</v>
+        <v>0.1892490581316173</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.5183693433357193</v>
+        <v>-0.005453617854170733</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>62.43313619004921</v>
+        <v>67.5149850071914</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1746343535508856</v>
+        <v>-0.02827807607930577</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2310335201671986</v>
+        <v>0.264885230566887</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.7741186316716193</v>
+        <v>-0.03490414252813952</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.069430026937654</v>
+        <v>-0.04660973493225438</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.197371297356474</v>
+        <v>0.2770012082070131</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.920385568139038</v>
+        <v>-0.1058115026946465</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>67.96447476989474</v>
+        <v>70.48801074329494</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.4874206221199424</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3764364915426457</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2.061388709630232</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>3.314075858776201</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1434266044240327</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>7.349146700135131</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>54.89280895284547</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>